--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90913</v>
+        <v>90919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90885</v>
+        <v>90891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92750</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92731</v>
+        <v>92737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90919</v>
+        <v>90925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90891</v>
+        <v>90897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92737</v>
+        <v>92743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1485,6 +1485,342 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128603128</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100771</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>584466</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6576162</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128603183</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>584512</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6576256</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128720869</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92768</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Eriksberg, Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>584505</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6576154</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kent Hellström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92762</v>
+        <v>92764</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92743</v>
+        <v>92745</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100771</v>
+        <v>100773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92764</v>
+        <v>92765</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92745</v>
+        <v>92746</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90928</v>
+        <v>90955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90900</v>
+        <v>90927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92765</v>
+        <v>92792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92746</v>
+        <v>92773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>90960</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90927</v>
+        <v>90932</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92792</v>
+        <v>92797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>90965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +917,12 @@
       <c r="E4" t="n">
         <v>5449</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -1021,7 +1012,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1127,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90932</v>
+        <v>90937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,7 +1245,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1363,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92778</v>
+        <v>92783</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1602,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1714,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90965</v>
+        <v>90969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90937</v>
+        <v>90941</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92783</v>
+        <v>92787</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90969</v>
+        <v>90974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90941</v>
+        <v>90946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92787</v>
+        <v>92792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90976</v>
+        <v>90981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92795</v>
+        <v>92800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128540259</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>128541719</v>
       </c>
       <c r="B3" t="n">
-        <v>90981</v>
+        <v>90987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128541582</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>128540334</v>
       </c>
       <c r="B6" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>128541932</v>
       </c>
       <c r="B8" t="n">
-        <v>92800</v>
+        <v>92808</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1481,7 +1481,7 @@
         <v>128603128</v>
       </c>
       <c r="B9" t="n">
-        <v>100857</v>
+        <v>100866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>128603183</v>
       </c>
       <c r="B10" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128720869</v>
       </c>
       <c r="B11" t="n">
-        <v>92838</v>
+        <v>92847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>92848</v>
+        <v>93208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,14 +915,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>6332770</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
@@ -991,6 +1000,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,6 +1822,112 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132590936</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101304</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>584517</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6576261</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93208</v>
+        <v>93214</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101304</v>
+        <v>101312</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93214</v>
+        <v>93224</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101312</v>
+        <v>101323</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93224</v>
+        <v>93225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101323</v>
+        <v>101324</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101324</v>
+        <v>101325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93225</v>
+        <v>93226</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>101327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93226</v>
+        <v>93228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101327</v>
+        <v>101329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93228</v>
+        <v>93229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101329</v>
+        <v>101330</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93229</v>
+        <v>93232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101330</v>
+        <v>101333</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101333</v>
+        <v>101334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -907,7 +907,7 @@
         <v>128542390</v>
       </c>
       <c r="B4" t="n">
-        <v>93233</v>
+        <v>93234</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>132590936</v>
       </c>
       <c r="B12" t="n">
-        <v>101334</v>
+        <v>101338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1255,7 +1255,7 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>93293</v>
+        <v>93300</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>133940601</v>
       </c>
       <c r="B13" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>133940711</v>
       </c>
       <c r="B14" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>133940733</v>
       </c>
       <c r="B15" t="n">
-        <v>110145</v>
+        <v>110152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128540259</v>
+        <v>128541932</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +721,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584511</v>
+        <v>584458</v>
       </c>
       <c r="R2" t="n">
-        <v>6576249</v>
+        <v>6576195</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +756,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +766,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128541719</v>
+        <v>128540334</v>
       </c>
       <c r="B3" t="n">
-        <v>90987</v>
+        <v>91333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,24 +804,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>2008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -832,13 +839,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584465</v>
+        <v>584512</v>
       </c>
       <c r="R3" t="n">
-        <v>6576187</v>
+        <v>6576247</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128542390</v>
+        <v>128541719</v>
       </c>
       <c r="B4" t="n">
-        <v>93234</v>
+        <v>91361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6332770</v>
+        <v>3286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584426</v>
+        <v>584465</v>
       </c>
       <c r="R4" t="n">
-        <v>6576203</v>
+        <v>6576187</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,7 +1007,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1019,56 +1025,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128541582</v>
+        <v>128603183</v>
       </c>
       <c r="B5" t="n">
-        <v>100847</v>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584491</v>
+        <v>584512</v>
       </c>
       <c r="R5" t="n">
-        <v>6576206</v>
+        <v>6576256</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,22 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,26 +1116,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128540334</v>
+        <v>128720869</v>
       </c>
       <c r="B6" t="n">
-        <v>90959</v>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,48 +1148,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2008</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>584512</v>
+        <v>584505</v>
       </c>
       <c r="R6" t="n">
-        <v>6576247</v>
+        <v>6576154</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1202,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,16 +1228,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1255,11 +1252,11 @@
         <v>128542111</v>
       </c>
       <c r="B7" t="n">
-        <v>93300</v>
+        <v>93307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1371,45 +1368,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128541932</v>
+        <v>133940648</v>
       </c>
       <c r="B8" t="n">
-        <v>92808</v>
+        <v>98219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>150</v>
+        <v>219815</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1417,13 +1407,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584458</v>
+        <v>584506</v>
       </c>
       <c r="R8" t="n">
-        <v>6576195</v>
+        <v>6576222</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,22 +1437,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,63 +1451,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128603128</v>
+        <v>133940711</v>
       </c>
       <c r="B9" t="n">
-        <v>100866</v>
+        <v>110159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Eriksberg, Eriksberg, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584466</v>
+        <v>584541</v>
       </c>
       <c r="R9" t="n">
-        <v>6576162</v>
+        <v>6576261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,22 +1543,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,68 +1557,68 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128603183</v>
+        <v>133940733</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>110159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Eriksberg, Eriksberg, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584512</v>
+        <v>584501</v>
       </c>
       <c r="R10" t="n">
-        <v>6576256</v>
+        <v>6576274</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,22 +1645,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,33 +1659,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128720869</v>
+        <v>133940875</v>
       </c>
       <c r="B11" t="n">
-        <v>92847</v>
+        <v>106358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,34 +1689,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>221157</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eriksberg, Eriksberg, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584505</v>
+        <v>584437</v>
       </c>
       <c r="R11" t="n">
-        <v>6576154</v>
+        <v>6576243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1778,22 +1747,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:56</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,33 +1761,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132590936</v>
+        <v>128540259</v>
       </c>
       <c r="B12" t="n">
-        <v>101338</v>
+        <v>101326</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1854,12 +1809,12 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1868,13 +1823,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584517</v>
+        <v>584511</v>
       </c>
       <c r="R12" t="n">
-        <v>6576261</v>
+        <v>6576249</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,12 +1853,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,29 +1877,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133940601</v>
+        <v>128541582</v>
       </c>
       <c r="B13" t="n">
-        <v>101396</v>
+        <v>101326</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1924,11 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1970,13 +1938,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584464</v>
+        <v>584491</v>
       </c>
       <c r="R13" t="n">
-        <v>6576227</v>
+        <v>6576206</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2000,12 +1968,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,72 +1992,63 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133940711</v>
+        <v>128603128</v>
       </c>
       <c r="B14" t="n">
-        <v>110152</v>
+        <v>101325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584541</v>
+        <v>584466</v>
       </c>
       <c r="R14" t="n">
-        <v>6576261</v>
+        <v>6576162</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,12 +2075,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,56 +2099,64 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133940733</v>
+        <v>132590936</v>
       </c>
       <c r="B15" t="n">
-        <v>110152</v>
+        <v>101403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2178,10 +2165,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584501</v>
+        <v>584517</v>
       </c>
       <c r="R15" t="n">
-        <v>6576274</v>
+        <v>6576261</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2208,12 +2195,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,6 +2225,427 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133940517</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>584437</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6576243</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133940601</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>584464</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6576227</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133940516</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>584437</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6576243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anja Hynynen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128542390</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93299</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>584426</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6576203</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128541932</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128540334</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128541719</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128603183</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128720869</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,6 +1395,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128542111</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1467,6 +1502,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940648</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940711</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940733</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940875</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128540259</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2007,6 +2067,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128541582</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2119,6 +2184,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128603128</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2225,6 +2295,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132590936</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940517</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2429,6 +2509,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940601</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940516</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2646,8 +2736,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128542390</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>